--- a/artfynd/A 25761-2024 artfynd.xlsx
+++ b/artfynd/A 25761-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,126 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126394653</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106247</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1651</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ölandskungsljus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Verbascum densiflorum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bertol.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Karsholms slott, 2,4 km SSV, Ölandskungsljus I, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>456279</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6216899</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österslöv</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>M-Kri-2536</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Markvägren samt gles tallskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Kjell-arne Olsson, Elna Hansson, Ulla Berglund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 25761-2024 artfynd.xlsx
+++ b/artfynd/A 25761-2024 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>126394653</v>
       </c>
       <c r="B3" t="n">
-        <v>106247</v>
+        <v>106256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
